--- a/data/trans_orig/P1420-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1420-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hemorroides en 2012</t>
+          <t>Población con diagnóstico de hemorroides en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24850</t>
+          <t>23636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>691730</t>
+          <t>691338</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>701627</t>
+          <t>701721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>680170</t>
+          <t>680488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>692839</t>
+          <t>692789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1375669</t>
+          <t>1376883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1392298</t>
+          <t>1392649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>22216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24731</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41320</t>
+          <t>41537</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>995880</t>
+          <t>995731</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010621</t>
+          <t>1010464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1004242</t>
+          <t>1004029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1020563</t>
+          <t>1020514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2005601</t>
+          <t>2005384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2028711</t>
+          <t>2028114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21226</t>
+          <t>21848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>26860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>747431</t>
+          <t>747413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756576</t>
+          <t>756586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>755948</t>
+          <t>755326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>769963</t>
+          <t>770398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1508214</t>
+          <t>1507937</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1524381</t>
+          <t>1524909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28470</t>
+          <t>29625</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35040</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>937045</t>
+          <t>937207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945880</t>
+          <t>946708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1023431</t>
+          <t>1022276</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1040977</t>
+          <t>1041172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1964600</t>
+          <t>1964746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1984202</t>
+          <t>1985041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43503</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>72167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66031</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102753</t>
+          <t>101819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3388286</t>
+          <t>3387605</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3409045</t>
+          <t>3408127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3480578</t>
+          <t>3482931</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3511595</t>
+          <t>3511910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6879124</t>
+          <t>6880058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6915846</t>
+          <t>6916837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hemorroides en 2016</t>
+          <t>Población con diagnóstico de hemorroides en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664242</t>
+          <t>664156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673747</t>
+          <t>673737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>662556</t>
+          <t>662988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671793</t>
+          <t>671858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1332080</t>
+          <t>1331883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343666</t>
+          <t>1344345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31345</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>38785</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1010764</t>
+          <t>1010783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1020477</t>
+          <t>1020514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1011568</t>
+          <t>1012194</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1030514</t>
+          <t>1030857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2027252</t>
+          <t>2026559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2049007</t>
+          <t>2048795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30814</t>
+          <t>30454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>738404</t>
+          <t>738538</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753709</t>
+          <t>754045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>769803</t>
+          <t>768887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>781902</t>
+          <t>781840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1513749</t>
+          <t>1514109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1532970</t>
+          <t>1533332</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22924</t>
+          <t>21078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40014</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914643</t>
+          <t>916489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931426</t>
+          <t>931645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1019176</t>
+          <t>1018951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1036412</t>
+          <t>1036016</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1941332</t>
+          <t>1941081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1964171</t>
+          <t>1964038</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>22827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>48388</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64010</t>
+          <t>60737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60726</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99935</t>
+          <t>102248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3345192</t>
+          <t>3345962</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3371974</t>
+          <t>3371523</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3480532</t>
+          <t>3483805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3511359</t>
+          <t>3511231</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6838957</t>
+          <t>6836644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6878166</t>
+          <t>6875346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1420-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1420-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>17825</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23636</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>691338</t>
+          <t>693012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>701721</t>
+          <t>701635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>680488</t>
+          <t>679225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>692789</t>
+          <t>692741</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1376883</t>
+          <t>1377828</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1392649</t>
+          <t>1392239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>21796</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,47 +1089,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>15052</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7661</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23571</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15052</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8459</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>24944</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18807</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41537</t>
+          <t>40260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>995731</t>
+          <t>996151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010464</t>
+          <t>1011345</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,49 +1202,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1013921</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1005402</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1021312</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>99,26%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1013921</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1004029</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1020514</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1848</t>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2005384</t>
+          <t>2006661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2028114</t>
+          <t>2028323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26860</t>
+          <t>26522</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>747413</t>
+          <t>748288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756586</t>
+          <t>756590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>755326</t>
+          <t>755705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770398</t>
+          <t>770565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1507937</t>
+          <t>1508275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1524909</t>
+          <t>1524659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>33896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>937207</t>
+          <t>935658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>946708</t>
+          <t>945825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1022276</t>
+          <t>1023256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1041172</t>
+          <t>1040442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1964746</t>
+          <t>1965744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1985041</t>
+          <t>1984590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39174</t>
+          <t>40208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>42142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72167</t>
+          <t>73299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65040</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101819</t>
+          <t>104383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3387605</t>
+          <t>3386571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3408127</t>
+          <t>3408622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3482931</t>
+          <t>3481799</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3511910</t>
+          <t>3512956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6880058</t>
+          <t>6877494</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6916837</t>
+          <t>6915823</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,47 +2693,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10009</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4125</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9851</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15756</t>
+          <t>15561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664156</t>
+          <t>663921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673737</t>
+          <t>673654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,49 +2806,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>668714</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>662830</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>671794</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>99,84%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>668714</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>662988</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>671858</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1310</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1331883</t>
+          <t>1332078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1344345</t>
+          <t>1343488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>30915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38785</t>
+          <t>40112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1010783</t>
+          <t>1010949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1020514</t>
+          <t>1020446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1012194</t>
+          <t>1011998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1030857</t>
+          <t>1031225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2026559</t>
+          <t>2025232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2048795</t>
+          <t>2047774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30454</t>
+          <t>31010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>738538</t>
+          <t>739127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754045</t>
+          <t>753944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>768887</t>
+          <t>770380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>781840</t>
+          <t>781823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1514109</t>
+          <t>1513553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1533332</t>
+          <t>1533229</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21078</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40265</t>
+          <t>40566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916489</t>
+          <t>915597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931645</t>
+          <t>931087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1018951</t>
+          <t>1018931</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1036016</t>
+          <t>1036158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1941081</t>
+          <t>1940780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1964038</t>
+          <t>1963624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>48829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>33634</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60737</t>
+          <t>63069</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63546</t>
+          <t>61837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102248</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3345962</t>
+          <t>3345521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3371523</t>
+          <t>3371235</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3483805</t>
+          <t>3481473</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3511231</t>
+          <t>3510908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6836644</t>
+          <t>6840469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6875346</t>
+          <t>6877055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
